--- a/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.05768061869363202</v>
+        <v>0.0308471549765246</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01631223036328101</v>
+        <v>0.1360782340310417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1601078379252359</v>
+        <v>0.05787661221161092</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.004292170471654282</v>
+        <v>0.09071277344902623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.1698158866904156</v>
+        <v>-0.1220668152252253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.1059718296081833</v>
+        <v>0.1133856270852031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.08462268451668212</v>
+        <v>-0.1158323095490752</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.01151863230082434</v>
+        <v>-0.1201505112505991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1633455108879262</v>
+        <v>0.131828667568476</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.04941546206717072</v>
+        <v>-0.04190954744146003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1166096077011469</v>
+        <v>-0.02825122251251309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.1066605805573901</v>
+        <v>0.1321170995023555</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0009930668275841225</v>
+        <v>0.08228117737840682</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.1214809047663973</v>
+        <v>-0.142739796444833</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.01733533221357222</v>
+        <v>0.0909812006138034</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1308398351106722</v>
+        <v>-0.1278850018630209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1180743846202023</v>
+        <v>0.1616700667814603</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0456786617008206</v>
+        <v>-0.0931545527259162</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.1219503724325452</v>
+        <v>-0.1012424590264533</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.113430791353429</v>
+        <v>0.1704849872659146</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.03624825655268595</v>
+        <v>0.009765978202519966</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.004619436593517939</v>
+        <v>0.06020602001199797</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.1008753104067015</v>
+        <v>-0.02343627826594651</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.02134238496047627</v>
+        <v>0.01137889969782654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.06117213479011466</v>
+        <v>-0.05365734479266229</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.1376061800378467</v>
+        <v>0.03609811305263376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1578695250854738</v>
+        <v>-0.1483070834246717</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.05537745464506883</v>
+        <v>-0.01320635682198716</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.1311736749843821</v>
+        <v>-0.03754417481393261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.07402479427473467</v>
+        <v>0.07563618512300581</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.1372587129398036</v>
+        <v>-0.1085789305231497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.1050317879867836</v>
+        <v>0.008012653072559</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1046291519144284</v>
+        <v>0.007678302837514883</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.08754581675495636</v>
+        <v>0.1435611877255104</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.08458267996948128</v>
+        <v>-0.04801643046542731</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01696379935659509</v>
+        <v>0.1291525506602118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.058233148611783</v>
+        <v>0.07377196187795203</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.00438120920171311</v>
+        <v>-0.03057044364925997</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.08905101673550601</v>
+        <v>-0.05888160383990922</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.1417227242104753</v>
+        <v>0.06512347069512635</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.07354662478400327</v>
+        <v>0.09525440178946659</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.1579092530654064</v>
+        <v>0.06100494701177409</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.08264806069437303</v>
+        <v>-0.1061670926542905</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.07520878407246352</v>
+        <v>-0.03909802949073012</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.1631048209772335</v>
+        <v>0.1611513009483448</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.02667483320831253</v>
+        <v>0.04866639715964916</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-0.02487323928554766</v>
+        <v>0.07670471487286132</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.1301323983601839</v>
+        <v>-0.0423896591600083</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.07769274978890787</v>
+        <v>0.05243763752178857</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.02213181590396622</v>
+        <v>-0.1070060750012781</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.04070231773399331</v>
+        <v>-0.1711513657876514</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.01676461018413858</v>
+        <v>-0.08465400152248785</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.007572759726191791</v>
+        <v>-0.1214313605701939</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.02530405519069066</v>
+        <v>-0.02484093947268695</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.1572856117772835</v>
+        <v>0.07836599017936625</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.09089310997496808</v>
+        <v>0.003619422237529597</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.1258247363099035</v>
+        <v>-0.03049864934191238</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.09311409622676466</v>
+        <v>0.07517459821201095</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.1505159353287557</v>
+        <v>0.05106687854475944</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.1423571026662598</v>
+        <v>-0.1410498591368458</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.08505810447012979</v>
+        <v>0.1121433198415725</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.1491359829482092</v>
+        <v>0.00142748318570568</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.158459435775751</v>
+        <v>-0.05367259622077453</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.03595253497244567</v>
+        <v>-0.09589859358194701</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.01002097389245265</v>
+        <v>-0.04970666916360653</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.06473255979531516</v>
+        <v>0.06740066113156069</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.1543437959006924</v>
+        <v>-0.06104335630314094</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.1565869003754287</v>
+        <v>-0.1321622540253947</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.09030924328187456</v>
+        <v>0.1026978396478294</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.06008097170303415</v>
+        <v>-0.1231870730455447</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.05084294444601414</v>
+        <v>-0.06717214114326991</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.07995306078556268</v>
+        <v>0.1160159754105772</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.01592544091550471</v>
+        <v>-0.05288139268173996</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.1727436608778307</v>
+        <v>-0.04332983959498186</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.0936892172872351</v>
+        <v>-0.1549966841718394</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.07691386666404229</v>
+        <v>-0.1322828438181421</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.07400946626704882</v>
+        <v>0.04345818550763943</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.02753985263576621</v>
+        <v>0.129671233975768</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.02013260456852567</v>
+        <v>-0.005614731270195226</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.1169319557047207</v>
+        <v>0.06918097094116392</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.02405967630278949</v>
+        <v>-0.1393691585823701</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-0.1281298514859859</v>
+        <v>0.1267841293628526</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.04217654344862813</v>
+        <v>-0.1320763184276938</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.03471367428490188</v>
+        <v>-0.07893558830746425</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.1206181852218002</v>
+        <v>0.11914036623573</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.1627731229021727</v>
+        <v>0.163058130725935</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.04426463302510612</v>
+        <v>0.05723481687538078</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.07115538568683802</v>
+        <v>-0.09950509190645103</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.1285602739919154</v>
+        <v>0.04459769229336225</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.03098761848438275</v>
+        <v>-0.1383419899165109</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.1245667209256358</v>
+        <v>-0.1774700406646903</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.1451141874989487</v>
+        <v>0.091950115843078</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.08987323716086398</v>
+        <v>-0.163472309883802</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1379075548798321</v>
+        <v>-0.1536477128977057</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.1532068385746931</v>
+        <v>0.06562689387823954</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.05664638753352498</v>
+        <v>-0.105419205025807</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.1519888635338905</v>
+        <v>-0.07509771775292914</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.122932458570143</v>
+        <v>-0.1512557050525144</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.06856341914355864</v>
+        <v>0.05038722442844745</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.09051056358523091</v>
+        <v>-0.001229390970995866</v>
       </c>
     </row>
   </sheetData>
